--- a/feedback_forms/006_net_promoter_score_questionnaire--feedback_forms.xlsx
+++ b/feedback_forms/006_net_promoter_score_questionnaire--feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2827,8 +2827,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2890,12 +2890,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -2941,12 +2941,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_dissatisfied'}</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2958,12 +2958,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'very_dissatisfied'}</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -2975,12 +2975,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'very_satisfied'}</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -2992,12 +2992,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_satisfied'}</t>
+          <t>somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3026,12 +3026,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_dissatisfied'}</t>
+          <t>somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -3043,12 +3043,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'very_dissatisfied'}</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'very_likely'}</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -3077,12 +3077,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_likely'}</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_unlikely'}</t>
+          <t>somewhat_unlikely</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'somewhat_unlikely'}</t>
+          <t>somewhat unlikely</t>
         </is>
       </c>
     </row>
@@ -3128,12 +3128,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'very_unlikely'}</t>
+          <t>very_unlikely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'very_unlikely'}</t>
+          <t>very unlikely</t>
         </is>
       </c>
     </row>
